--- a/02_加值成品/九上/九上2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-4 萬有引力與重力　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上2-4 萬有引力與重力　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>任意兩物體間互相吸引的力是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>萬有引力</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>普遍</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>地球對物體的萬有引力表現為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>向下</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>重力的方向是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>指向地心</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>向下</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>質量越大萬有引力？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>指向地心</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>距離越近萬有引力？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>越小</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>越強</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>物體所受重力的大小是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>力</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>月球繞地球靠什麼力？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>萬有引力</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>越小</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>重量會隨重力改變嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>會</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>指向地心</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>非質量</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>物體在地球上落下是受什麼力？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>向下</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>萬有引力隨距離增加會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>變小</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>指向地心</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-4 萬有引力與重力　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上2-4 萬有引力與重力　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>只有地球有引力嗎？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>所有物體</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>太空人失重代表沒引力嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>同時落地</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>失重狀態</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>忽略空氣鐵球與羽毛同高落下？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>同時落地</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>等加速</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>月球重力約地球的六分之一,質量？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>指向地心</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>同時落地</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>質量恆定</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>地球繞太陽靠什麼力？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>會</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>萬有引力</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>向心</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>物體離地球越遠重力？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>越小</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>重量與質量哪個會變？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>引力較弱</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>隨重力</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>潮汐主要受哪個天體引力？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>越小</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>月球</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>引力</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>同一物體在地球與月球何者較重？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>指向地心</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>地球</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>重力大</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>月球對地球也有引力嗎？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>指向地心</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>相互</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-4 萬有引力與重力　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上2-4 萬有引力與重力　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何月球上體重較輕但質量不變？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>重力加速度相同</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>與站同步自由下落呈失重</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>大小相等(作用反作用)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>月球重力小重量小、質量與位置無關</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>衛星繞地球不掉下來因為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>與站同步自由下落呈失重</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>萬有引力提供向心力維持圓周運動</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>與站同步繞地自由下落(失重)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>受地球重力吸引</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>向心</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用萬有引力解釋潮汐現象？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>與站同步自由下落呈失重</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>大小相等(作用反作用)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>月球對海水引力造成漲退</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>受地球重力吸引</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>兩物質量增加距離不變引力如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>越小</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>增大</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>指向地心</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>正比質量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>太空站中物體漂浮是因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>月球對海水引力造成漲退</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>重力加速度相同</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>大小相等(作用反作用)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>與站同步自由下落呈失重</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>失重</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>自由落體忽略空氣為何同時落地？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>月球對海水引力造成漲退</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>月球重力小重量小、質量與位置無關</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>受地球重力吸引</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>重力加速度相同</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>等加速</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>地球與蘋果的引力誰施給誰較大？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>大小相等(作用反作用)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>月球重力小重量小、質量與位置無關</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>與站同步繞地自由下落(失重)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>萬有引力提供向心力維持圓周運動</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>第三定律</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何行星離太陽越遠公轉越慢？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>引力較弱</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>萬有引力</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何拋出的球最終會落地？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>月球重力小重量小、質量與位置無關</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>月球對海水引力造成漲退</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>與站同步自由下落呈失重</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>受地球重力吸引</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>太空人在太空站漂浮是因為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>與站同步繞地自由下落(失重)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>重力加速度相同</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>月球重力小重量小、質量與位置無關</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>萬有引力提供向心力維持圓周運動</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>失重</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>普遍</t>
+          <t>普遍：只要有質量的物體之間,彼此就會互相吸引,這就是萬有引力</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>向下</t>
+          <t>向下：地球用萬有引力吸引我們,這股力在地表就是我們感受到的重力</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>向下</t>
+          <t>向下：重力永遠指向地球的中心,所以我們感覺它是往下拉</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：物體的質量越大,產生的萬有引力也會跟著變大</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>越強</t>
+          <t>越強：兩物體靠得越近,彼此之間的萬有引力就會越強</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>力</t>
+          <t>力：重量指的就是物體受到重力吸引的力量大小</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>維持</t>
+          <t>維持：地球和月球間的萬有引力,把月球拉住讓它繞著地球轉</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>非質量</t>
+          <t>非質量：重量是重力造成的,重力改變重量就跟著改變,但質量不會變</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>向下</t>
+          <t>向下：地球會吸引地表附近的物體,這股向下的吸引力叫做重力,使物體自然落下</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>距離</t>
+          <t>距離：根據萬有引力定律,兩物體間的距離越遠,彼此的吸引力就越小</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>所有物體</t>
+          <t>所有物體：只要有質量的東西都有引力,不是只有地球才有</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>失重狀態</t>
+          <t>失重狀態：太空人還是受地球引力,只是和太空站一起自由落下才感覺不到重量</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>等加速</t>
+          <t>等加速：沒有空氣阻力時,不管多重的東西重力加速度都一樣,會同時落地</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>質量恆定</t>
+          <t>質量恆定：物體換到月球只是所受重力變小,本身的質量完全不會改變</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>向心</t>
+          <t>向心：太陽和地球間的萬有引力,提供讓地球繞圈公轉所需要的力</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>距離</t>
+          <t>距離：距離地球越遠,受到的萬有引力也就是重力就會越來越小</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>隨重力</t>
+          <t>隨重力：換到不同星球重力不同,重量會跟著變,但質量永遠不變</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>引力</t>
+          <t>引力：月球對地球海水的引力是造成潮汐漲退最主要的原因</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>重力大</t>
+          <t>重力大：地球質量比月球大很多,重力也比較大,同一物體在地球上受到的重力(重量)比在月球上大</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>相互</t>
+          <t>相互：萬有引力是互相的,月球一樣會吸引地球,只是因為月球質量小,吸引力相對較小</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：重量是重力大小造成的,月球重力小所以體重輕,但身體含的物質量不會因位置改變</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>向心</t>
+          <t>向心：地球對衛星的萬有引力,剛好提供讓衛星持續繞圈所需要的力,所以不會掉下來</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：月球的萬有引力把靠近它那一側的海水拉起來,造成海水漲潮退潮的現象</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>正比質量</t>
+          <t>正比質量：距離維持不變的情況下,只要質量變大,兩者間的萬有引力就會跟著變大</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>失重</t>
+          <t>失重：太空站和裡面的物體一起繞地球自由落下,彼此沒有相對運動,所以看起來像漂浮</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>等加速</t>
+          <t>等加速：沒有空氣阻力干擾時,任何物體受到的重力加速度都相同,所以會同時落地</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>第三定律</t>
+          <t>第三定律：地球吸引蘋果的力,跟蘋果吸引地球的力,依照牛頓第三定律大小是相等的</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>萬有引力</t>
+          <t>萬有引力：離太陽越遠受到的引力越弱,能提供的向心力較小,行星公轉速度也會變慢</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>重力：球離開手之後,唯一持續作用的主要力就是地球的重力,重力把球向下拉,最後使球落地</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>失重</t>
+          <t>失重：太空站與太空人都以相同速度繞地球運動,兩者一起自由落下,彼此之間感受不到重力,所以呈現漂浮的失重狀態</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上2-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-4_三種難度測驗卷.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>越大</t>
+          <t>指向地心</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>引力較弱</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>重量</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>引力較弱</t>
+          <t>指向地心</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>重力</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>越小</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>會</t>
+          <t>重量</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>變小</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>萬有引力</t>
+          <t>同時落地</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>指向地心</t>
+          <t>越小</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>會</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
